--- a/出口目标.xlsx
+++ b/出口目标.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\grok知识库\excel_s\us_weekly_export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA751DF7-7FE0-4296-B924-CFEFBECED518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA586C7-D6A2-4379-898C-CEDA0464272A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12266" xr2:uid="{27E98898-5729-459E-A13C-00F14361E215}"/>
   </bookViews>
@@ -549,16 +549,16 @@
         <v>53864000</v>
       </c>
       <c r="I2" s="2">
-        <v>46266000</v>
+        <v>46350000</v>
       </c>
       <c r="J2" s="2">
-        <v>51227000</v>
+        <v>51495000</v>
       </c>
       <c r="K2" s="2">
-        <v>41368000</v>
+        <v>41243000</v>
       </c>
       <c r="L2" s="2">
-        <v>45858000</v>
+        <v>46130000</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
@@ -636,10 +636,10 @@
         <v>72966000</v>
       </c>
       <c r="K6" s="2">
-        <v>86999000</v>
+        <v>87106000</v>
       </c>
       <c r="L6" s="2">
-        <v>83189000</v>
+        <v>83824000</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
